--- a/XBRL-template-MPERS/Company/11-Notes-CorporateInfo.xlsx
+++ b/XBRL-template-MPERS/Company/11-Notes-CorporateInfo.xlsx
@@ -442,49 +442,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on corporate information [abstract]</t>
+          <t>Disclosure on corporate information</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Corporate information [abstract]</t>
+          <t>Corporate information</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Disclosure of corporate information [textblock]</t>
+          <t>Disclosure of corporate information</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financial reporting status [abstract]</t>
+          <t>Financial reporting status</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Explanation of reasons for the restatement of previous financial statements figures [textblock]</t>
+          <t>Explanation of reasons for the restatement of previous financial statements figures</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Explanation of reasons for the reclassification of previous financial statements figures [textblock]</t>
+          <t>Explanation of reasons for the reclassification of previous financial statements figures</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Explanation of reasons for using longer or shorter reporting period [textblock]</t>
+          <t>Explanation of reasons for using longer or shorter reporting period</t>
         </is>
       </c>
     </row>

--- a/XBRL-template-MPERS/Company/11-Notes-CorporateInfo.xlsx
+++ b/XBRL-template-MPERS/Company/11-Notes-CorporateInfo.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,14 +451,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on corporate information</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Corporate information</t>
         </is>
@@ -461,7 +472,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Financial reporting status</t>
         </is>
